--- a/site/public/admin/event2027/files/snu2027_evaluation_scoresheet.xlsx
+++ b/site/public/admin/event2027/files/snu2027_evaluation_scoresheet.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>새 동창회의 정체성·비전을 행사 전체에 일관된 메시지로 풀어냄</t>
+          <t>새 동문회의 정체성·비전을 행사 전체에 일관된 메시지로 풀어냄</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
